--- a/Tablas.xlsx
+++ b/Tablas.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diego\OneDrive\Documentos\UCJC\UCJC4\Diseño seguro y fiable\PEC1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diego\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A3DCD3-A890-4BF8-B18A-41FE4A7F2397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3547E01-C4E0-48D6-99FF-7577F80D1EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="5" xr2:uid="{FC4A1DD3-E17F-4E74-A11E-2C2822CC6DC1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="1" xr2:uid="{FC4A1DD3-E17F-4E74-A11E-2C2822CC6DC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Identificación de activos" sheetId="1" r:id="rId1"/>
     <sheet name="Identificación de amenazas" sheetId="2" r:id="rId2"/>
-    <sheet name=" Mapeo al OWASP Top 10" sheetId="3" r:id="rId3"/>
-    <sheet name="Plan de tratamiento de amenazas" sheetId="4" r:id="rId4"/>
-    <sheet name="Requisitos de seguridad" sheetId="5" r:id="rId5"/>
-    <sheet name="Marco de referencia" sheetId="6" r:id="rId6"/>
+    <sheet name="Análisis de privacidad " sheetId="9" r:id="rId3"/>
+    <sheet name="Priorizacion de amenazas" sheetId="10" r:id="rId4"/>
+    <sheet name=" Mapeo al OWASP Top 10" sheetId="3" r:id="rId5"/>
+    <sheet name="Plan de tratamiento de amenazas" sheetId="4" r:id="rId6"/>
+    <sheet name="Requisitos de seguridad" sheetId="5" r:id="rId7"/>
+    <sheet name="Registro de cadena de suministr" sheetId="11" r:id="rId8"/>
+    <sheet name="Riesgos del chatbot LLM" sheetId="12" r:id="rId9"/>
+    <sheet name="Marco de referencia" sheetId="6" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="335">
   <si>
     <t>Activo</t>
   </si>
@@ -85,18 +89,6 @@
     <t>Consecuencia de negocio</t>
   </si>
   <si>
-    <t>Minimo(1):Spoofing,Tampering</t>
-  </si>
-  <si>
-    <t>Information Disclosure</t>
-  </si>
-  <si>
-    <t>Denial Service</t>
-  </si>
-  <si>
-    <t>Elevation of privilege</t>
-  </si>
-  <si>
     <t>ID Amenaza</t>
   </si>
   <si>
@@ -106,9 +98,6 @@
     <t>Debilidad concreta que justifica la correspondencia</t>
   </si>
   <si>
-    <t>Respuesta</t>
-  </si>
-  <si>
     <t>Enunciado Requisito</t>
   </si>
   <si>
@@ -169,30 +158,15 @@
     <t>PROMPT</t>
   </si>
   <si>
-    <t>DNI, pasaporte, datos biométricos, dirección, email y número de teléfono de los usuarios</t>
-  </si>
-  <si>
     <t>Responsable de Cumplimiento Normativo</t>
   </si>
   <si>
-    <t>MUY ALTO: Su divulgación masiva constituye una violación grave del GDPR, con sanciones administrativas de hasta 20M€, además de daño reputacional y posible fraude de identidad</t>
-  </si>
-  <si>
-    <t>MEDIO: Si no estan disponibles los datos personales no se pueden registrar nuevos usuairos ni acceder a los datos los usuairos ya registrados puesto que no pueden iniciar sesión</t>
-  </si>
-  <si>
     <t>ALTO: La modificación de estos datos permite suplantar la identidad</t>
   </si>
   <si>
     <t xml:space="preserve">Datos personales de usuarios  y documentación KYC </t>
   </si>
   <si>
-    <t>MUY ALTO: Si se filtran las credenciales el sistema estaria comrometido</t>
-  </si>
-  <si>
-    <t>BAJO: Una caída del servicio de autenticación impediria el acceso pero no es un fallo critico</t>
-  </si>
-  <si>
     <t>Balances de usuarios y activos en custodia</t>
   </si>
   <si>
@@ -208,9 +182,6 @@
     <t>CRÍTICO: La modificación de activos, permite el robo de dinero</t>
   </si>
   <si>
-    <t>MUY ALTO: Si no esta disponible la consulta de balances, se paralizan toda la operaciones de trading, depósitos y retiradas</t>
-  </si>
-  <si>
     <t>Disponibilidad del servicio (uptime)</t>
   </si>
   <si>
@@ -220,12 +191,6 @@
     <t>Director de Operaciones</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>CRÍTICO: La caída del servicio provoca pérdida de confianza, fuga de clientes  y posibles pérdidas</t>
-  </si>
-  <si>
     <t>Reputación corporativa</t>
   </si>
   <si>
@@ -235,30 +200,15 @@
     <t>Dirección General</t>
   </si>
   <si>
-    <t>MUY ALTO: Puede dañar la confianza y llevar al fracaso del negocio</t>
-  </si>
-  <si>
     <t>Registros de auditoría y logs</t>
   </si>
   <si>
-    <t>Actividad del sistema, intentos de acceso, operaciones realizadas y accesos de los admin</t>
-  </si>
-  <si>
     <t>Auditor Interno</t>
   </si>
   <si>
-    <t>MEDIO: Los logs contienen datos personales (IPs) y su adquisición puede incumplir el GDPR</t>
-  </si>
-  <si>
     <t>CRÍTICO: La manipulación o eliminación de logs complica la investigación forense tras un incidente</t>
   </si>
   <si>
-    <t>ALTO: La eliminación o modificación de los logs puede evitar encontrar un fallo en el sistema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUY ALTO: La modificación de las claves de acceso puede llevar a cabo la perdida de la cuenta </t>
-  </si>
-  <si>
     <t>Credenciales de acceso de usuario y del sistema</t>
   </si>
   <si>
@@ -268,15 +218,6 @@
     <t>Secretos criptográficos asociados a la autenticación multifactor</t>
   </si>
   <si>
-    <t xml:space="preserve"> Responsable de Seguridad de Aplicaciones</t>
-  </si>
-  <si>
-    <t>MUY ALTO: La exposición de hashes permite ataques de fuerza bruta para recuperar contraseñas</t>
-  </si>
-  <si>
-    <t>BAJO: Una caída del servicio de autenticación impide el acceso,</t>
-  </si>
-  <si>
     <t>ALTO: La modificación o desactivación de un proceso de doble autentificación por un atacante puede derivar en la perdidad de la cuenta</t>
   </si>
   <si>
@@ -295,9 +236,6 @@
     <t>ALTO: La modificación de una clave de API puede denegar el servicio a componentes legítimos o redirigir comunicaciones</t>
   </si>
   <si>
-    <t>MEDIO: La indisponibilidad de una clave puede interrumpir la comunicación entre servicios</t>
-  </si>
-  <si>
     <t>Identificación de activos</t>
   </si>
   <si>
@@ -374,13 +312,1459 @@
   </si>
   <si>
     <t>Diagrama DFD nivel 0 y 1(Que son breve introducción)</t>
+  </si>
+  <si>
+    <t>MUY ALTO: Su divulgación masiva constituye una violación grave del GDPR, con sanciones administrativas es de hasta 20M€, además de daño reputacional y posible fraude de identidad</t>
+  </si>
+  <si>
+    <t>Responsable de Seguridad de Aplicaciones</t>
+  </si>
+  <si>
+    <t>MUY ALTO: Si se filtran las credenciales el sistema estaria comprometido</t>
+  </si>
+  <si>
+    <t>MUY ALTO: La modificación de las claves de acceso puede llevar a cabo la perdida de la cuenta y dinero disponible en la cuenta</t>
+  </si>
+  <si>
+    <t>Actividad del sistema, intentos de acceso, operaciones realizadas y accesos de los admin, modificación de datos y permisos</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>MEDIO: La indisponibilidad impide la detección de fraude e incumple MiCA</t>
+  </si>
+  <si>
+    <t>MUY ALTO: La exposición del secreto TOTP (Time-based One-Time Password) permite generar códigos válidos y comprometer cuentas</t>
+  </si>
+  <si>
+    <t>Motor de trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Componente central encargado de gestionar el ciclo completo de órdenes: recepción, validación, ejecución y actualizacion de balances. </t>
+  </si>
+  <si>
+    <t>Responsable Financiero / Equipo de Arquitectura de Software</t>
+  </si>
+  <si>
+    <t>MEDIO: Procesa información de órdenes y cantidades que, si se expone, puede revelar patrones de actividad o estrategias de los usuarios.</t>
+  </si>
+  <si>
+    <t>CRÍTICO: Cualquier manipulación (alteración del matching, precios, órdenes o explotación de condiciones de carrera) puede provocar doble gasto, pérdidas económicas irreversibles y discrepancias en balances.</t>
+  </si>
+  <si>
+    <t>MUY ALTO: Si el motor cae, se paralizan compras/ventas, depósitos y retiradas, deteniendo completamente la operativa y generando pérdidas económicas y reputacionales.</t>
+  </si>
+  <si>
+    <t>Motor de Trading (F‑06, F‑09)</t>
+  </si>
+  <si>
+    <t>T — Tampering (Manipulación)</t>
+  </si>
+  <si>
+    <t>Un atacante explota una condición de carrera enviando múltiples solicitudes de retirada simultáneas antes de que el saldo se actualice, consiguiendo un doble gasto. También podría alterar parámetros de órdenes si el motor no valida adecuadamente entradas.</t>
+  </si>
+  <si>
+    <t>Balances de usuarios y activos en custodia / Motor de Trading</t>
+  </si>
+  <si>
+    <t>Falta de control transaccional estricto.
+Ausencia de bloqueo optimista/pesimista.
+Validaciones insuficientes de órdenes.</t>
+  </si>
+  <si>
+    <t>Descuadres en balances, duplicación de retiradas, integridad financiera comprometida.</t>
+  </si>
+  <si>
+    <t>Pérdidas económicas directas e irreversibles, impacto regulatorio crítico y posible insolvencia.</t>
+  </si>
+  <si>
+    <t>Servicio de Autenticación (F‑01, F‑02, F‑03a, F‑03b)</t>
+  </si>
+  <si>
+    <t>T — Tampering (S — Spoofing (Suplantación de identidad)Manipulación)</t>
+  </si>
+  <si>
+    <t>Un atacante utiliza credenciales filtradas o débiles para autenticarse como un usuario legítimo a través del API Gateway, saltándose el control MFA si este no está correctamente configurado o si los secretos OTP han sido expuestos.</t>
+  </si>
+  <si>
+    <t>Credenciales de acceso del usuario / Factores MFA</t>
+  </si>
+  <si>
+    <t>Ausencia de limitación de intentos.
+Contraseñas débiles.
+Configuración insuficiente del MFA.
+Falta de detección de patrones de acceso anómalos.</t>
+  </si>
+  <si>
+    <t>Acceso completo a la cuenta del usuario, incluyendo compras, ventas y retiradas.</t>
+  </si>
+  <si>
+    <t>Pérdida irreversible de fondos, reclamaciones regulatorias, pérdida de confianza y daño reputacional.</t>
+  </si>
+  <si>
+    <t>Servicio KYC (F‑04, F‑05a, F‑05b)</t>
+  </si>
+  <si>
+    <t>I — Information Disclosure (Divulgación de información)</t>
+  </si>
+  <si>
+    <t>Un atacante intercepta o accede indebidamente a documentos KYC enviados al proveedor externo, exponiendo datos biométricos, DNI, pasaporte y fotografías del usuario.</t>
+  </si>
+  <si>
+    <t>Datos personales y documentación KYC</t>
+  </si>
+  <si>
+    <t>Envío no cifrado o mala configuración TLS.
+Dependencia de un proveedor externo sin controles robustos.
+Almacenamiento temporal inseguro en el microservicio.</t>
+  </si>
+  <si>
+    <t>Exposición de datos extremadamente sensibles, incumplimiento del GDPR/MiCA.</t>
+  </si>
+  <si>
+    <t>Sanciones administrativas, pérdida de confianza del usuario, riesgo legal y daño reputacional severo.</t>
+  </si>
+  <si>
+    <t>Motor de Trading → BD de Auditoría (F‑10, F‑11)</t>
+  </si>
+  <si>
+    <t>R — Repudiation (Repudio)</t>
+  </si>
+  <si>
+    <t>Un usuario realiza una operación de compra o retirada, pero debido a una mala configuración del sistema de logs o a una escritura incompleta en la BD de Auditoría, después niega haber ejecutado dicha operación.</t>
+  </si>
+  <si>
+    <t>Falta de registros completos o inmutables
+Logs almacenados en sistemas sin integridad verificable
+No sincronización entre motores de trading y auditoría</t>
+  </si>
+  <si>
+    <t>Imposibilidad de determinar la secuencia real de eventos.</t>
+  </si>
+  <si>
+    <t>Conflictos legales, incumplimiento de MiCA, riesgo de fraude y sanciones regulatorias.</t>
+  </si>
+  <si>
+    <t>Chatbot LLM (F‑14)</t>
+  </si>
+  <si>
+    <t>Un usuario malintencionado emplea prompt injection para obligar al chatbot LLM a revelar datos privados de otros usuarios o información interna del sistema.</t>
+  </si>
+  <si>
+    <t>Datos personales de usuarios / Reputación corporativa</t>
+  </si>
+  <si>
+    <t>Falta de filtros y sanitización en el prompt
+Modelo LLM con acceso excesivo al contexto del usuario
+Ausencia de políticas de redacción segura</t>
+  </si>
+  <si>
+    <t>Revelación de datos confidenciales o internas.</t>
+  </si>
+  <si>
+    <t>Incumplimiento GDPR/MiCA, daño reputacional, pérdida de confianza.</t>
+  </si>
+  <si>
+    <t>API Gateway (F‑01, F‑06)</t>
+  </si>
+  <si>
+    <t>D — Denial of Service (DoS)</t>
+  </si>
+  <si>
+    <t>Un atacante envía miles de peticiones simultáneas contra el API Gateway, agotando los recursos disponibles e impidiendo a usuarios legítimos acceder o realizar operaciones.</t>
+  </si>
+  <si>
+    <t>Falta de rate limiting efectivo
+Falta de detección y bloqueo de tráfico anómalo
+Dimensionamiento insuficiente</t>
+  </si>
+  <si>
+    <t>Caída o degradación severa del servicio.</t>
+  </si>
+  <si>
+    <t>Interrupción total de operaciones, pérdidas económicas y fuga de clientes.</t>
+  </si>
+  <si>
+    <t>Panel de administración (F‑12, F‑13)</t>
+  </si>
+  <si>
+    <t>E — Elevation of Privilege</t>
+  </si>
+  <si>
+    <t>Un empleado de soporte o un atacante que obtiene acceso a la VPN corporativa explota un control débil y obtiene privilegios administrativos, permitiendo modificar cuentas, saldos o datos críticos.</t>
+  </si>
+  <si>
+    <t>Registros de auditoría / Balances / Reputación corporativa</t>
+  </si>
+  <si>
+    <t>Ausencia de separación de funciones (SoD)
+Falta de MFA reforzado en el panel admin
+No validación de roles y permisos</t>
+  </si>
+  <si>
+    <t>Acciones administrativas no autorizadas.</t>
+  </si>
+  <si>
+    <t>Robo de fondos, fraude interno y compromisos regulatorios.</t>
+  </si>
+  <si>
+    <t>BD de usuarios (F‑03a, F‑03b, F‑08)</t>
+  </si>
+  <si>
+    <t>T — Tampering</t>
+  </si>
+  <si>
+    <t>Un atacante o empleado interno modifica manualmente los datos de configuración de MFA o credenciales, permitiendo acceder a cuentas sin autorización.</t>
+  </si>
+  <si>
+    <t>Credenciales de usuario / Configuración MFA</t>
+  </si>
+  <si>
+    <t>Falta de controles de integridad en la BD
+Permisos excesivos en microservicios
+Ausencia de cifrado en reposo</t>
+  </si>
+  <si>
+    <t>Modificación no autorizada de identidades y accesos.</t>
+  </si>
+  <si>
+    <t>Suplantación de usuarios, fraude y riesgo regulatorio.</t>
+  </si>
+  <si>
+    <t>Servicio Wallet (F‑07, F‑08)</t>
+  </si>
+  <si>
+    <t>D — Denial of Service</t>
+  </si>
+  <si>
+    <t>Un atacante fuerza miles de solicitudes de retirada por usuario o automatiza transacciones falsas, saturando el servicio wallet e impidiendo la firma de transacciones legítimas.</t>
+  </si>
+  <si>
+    <t>Disponibilidad de fondos / Servicio Wallet</t>
+  </si>
+  <si>
+    <t>Falta de mecanismos de rate control
+Ausencia de colas priorizadas
+No validación de límites de uso</t>
+  </si>
+  <si>
+    <t>Servicio wallet paralizado, órdenes sin procesar.</t>
+  </si>
+  <si>
+    <t>Retrasos críticos, usuarios bloqueados, mala experiencia y daño reputacional.</t>
+  </si>
+  <si>
+    <t>BD de Auditoría (F‑11, F‑13)</t>
+  </si>
+  <si>
+    <t>R — Repudiation</t>
+  </si>
+  <si>
+    <t>Un atacante interno con acceso elevado borra o modifica entradas en la BD de auditoría para ocultar acciones fraudulentas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de inmutabilidad
+No existen hash o firmas digitales de los logs
+Accesos con permisos excesivos
+</t>
+  </si>
+  <si>
+    <t>Evidencias alteradas o inexistentes.</t>
+  </si>
+  <si>
+    <t>Imposibilidad de investigar incidentes, incumplimiento regulatorio y riesgo de sanciones.</t>
+  </si>
+  <si>
+    <t>Impacto</t>
+  </si>
+  <si>
+    <t>RP‑01</t>
+  </si>
+  <si>
+    <t>Personal interno accede a documentos KYC sin necesidad operativa</t>
+  </si>
+  <si>
+    <t>Disclosure / Confidencialidad</t>
+  </si>
+  <si>
+    <t>Robo de identidad, violación GDPR, alta sensibilidad</t>
+  </si>
+  <si>
+    <t>RBAC estricto, auditoría de accesos, cifrado total</t>
+  </si>
+  <si>
+    <t>RP‑02</t>
+  </si>
+  <si>
+    <t>Correlación entre identidad real y direcciones públicas de wallet</t>
+  </si>
+  <si>
+    <t>Linkability / Identifiability</t>
+  </si>
+  <si>
+    <t>Pérdida de anonimato financiero</t>
+  </si>
+  <si>
+    <t>Direcciones rotativas, minimización de datos, ocultar direcciones completas</t>
+  </si>
+  <si>
+    <t>RP‑03</t>
+  </si>
+  <si>
+    <t>Disclosure / Detectability</t>
+  </si>
+  <si>
+    <t>Categoría de privacidad / LINDDUN</t>
+  </si>
+  <si>
+    <t>Impacto para el usuario</t>
+  </si>
+  <si>
+    <t>Medida de control propuesta</t>
+  </si>
+  <si>
+    <t>Fuga de datos personales, riesgo regulatorio</t>
+  </si>
+  <si>
+    <t>Filtro previo, limitación de contexto, redacción segura</t>
+  </si>
+  <si>
+    <t>RP‑04</t>
+  </si>
+  <si>
+    <t>Conservación de datos más tiempo del legal</t>
+  </si>
+  <si>
+    <t>Non‑Compliance / Privacy by Design</t>
+  </si>
+  <si>
+    <t>Exposición prolongada y tratamiento indebido</t>
+  </si>
+  <si>
+    <t>Políticas automáticas de retención/eliminación y control de backups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <t>Probabilidad</t>
+  </si>
+  <si>
+    <t>Nivel de Riesgo</t>
+  </si>
+  <si>
+    <t>Justificación breve</t>
+  </si>
+  <si>
+    <t>T‑02</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>CRÍTICO</t>
+  </si>
+  <si>
+    <t>T‑01</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>T‑03</t>
+  </si>
+  <si>
+    <t>ALTO</t>
+  </si>
+  <si>
+    <t>T‑07</t>
+  </si>
+  <si>
+    <t>T‑10</t>
+  </si>
+  <si>
+    <t>Explotar condiciones de carrera o manipulación de órdenes es técnicamente viable si no hay controles transaccionales fuertes.</t>
+  </si>
+  <si>
+    <t>Los ataques de credential stuffing y acceso sin MFA reforzado son muy comunes.</t>
+  </si>
+  <si>
+    <t>Intercambio con terceros y datos biométricos → riesgo real si hay mala configuración TLS o proveedores débiles.</t>
+  </si>
+  <si>
+    <t>Si un empleado o atacante obtiene acceso a la VPN, podría elevar privilegios si los roles no están bien segmentados.</t>
+  </si>
+  <si>
+    <t>Sin controles de integridad, hashes o logs inmutables, un insider podría eliminar pruebas.</t>
+  </si>
+  <si>
+    <t>A07 — Fallos de autenticación</t>
+  </si>
+  <si>
+    <t>Controles de autenticación débiles, falta de limitación de intentos, y uso insuficiente de MFA permiten a un atacante autenticarse como un usuario legítimo.</t>
+  </si>
+  <si>
+    <t>A08 — Fallos de integridad en software y datos</t>
+  </si>
+  <si>
+    <t>El motor de trading carece de controles transaccionales robustos y validaciones, lo que permite manipulación de órdenes y condiciones de carrera.</t>
+  </si>
+  <si>
+    <t>A04 — Fallos criptográficos</t>
+  </si>
+  <si>
+    <t>Riesgo de cifrado mal configurado en tránsito o en reposo, y dependencia del proveedor externo para tratamiento de datos altamente sensibles.</t>
+  </si>
+  <si>
+    <t>A09 — Fallos de logging y monitorización</t>
+  </si>
+  <si>
+    <t>Registros de auditoría incompletos o no inmutables permiten negar operaciones y dificultan investigación forense.</t>
+  </si>
+  <si>
+    <t>A05 — Inyección</t>
+  </si>
+  <si>
+    <t>A10 — Tratamiento incorrecto de condiciones excepcionales</t>
+  </si>
+  <si>
+    <t>Falta de rate‑limiting, mala gestión de sobrecargas y ausencia de defensas contra abuse de tráfico.</t>
+  </si>
+  <si>
+    <t>A01 — Control de acceso defectuoso</t>
+  </si>
+  <si>
+    <t>Roles mal definidos y controles insuficientes permiten que un usuario obtenga privilegios administrativos no autorizados.</t>
+  </si>
+  <si>
+    <t>A02 — Configuración insegura</t>
+  </si>
+  <si>
+    <t>Permisos excesivos, mala configuración de la base de datos y falta de validaciones permiten modificar MFA o credenciales.</t>
+  </si>
+  <si>
+    <t>A06 — Diseño inseguro</t>
+  </si>
+  <si>
+    <t>Ausencia de colas priorizadas, límites de uso y validación de solicitudes impide resistencia a saturación del servicio.</t>
+  </si>
+  <si>
+    <t>Sin integridad garantizada (hashes, firmas digital, WORM), los logs pueden ser alterados o eliminados para ocultar actividad maliciosa.</t>
+  </si>
+  <si>
+    <t>Amenaza</t>
+  </si>
+  <si>
+    <t>Estrategia (Mitigar / Eliminar / Transferir / Aceptar)</t>
+  </si>
+  <si>
+    <t>Justificación</t>
+  </si>
+  <si>
+    <t>Manipulación del Motor de Trading</t>
+  </si>
+  <si>
+    <t>MITIGAR</t>
+  </si>
+  <si>
+    <t>La manipulación de órdenes o condiciones de carrera puede causar pérdidas financieras irreversibles. Dado que el motor de trading es crítico y no puede eliminarse, se deben mitigar los riesgos mediante: controles transaccionales, bloqueo optimista/pesimista, validación estricta de entradas y pruebas de concurrencia. Esta amenaza no puede aceptarse ni transferirse, ya que impacta directamente en fondos de usuarios y obligaciones reguladas.</t>
+  </si>
+  <si>
+    <t>Suplantación de identidad (Spoofing)</t>
+  </si>
+  <si>
+    <t>El compromiso de credenciales o MFA impacta directamente en el dinero de los usuarios. Es obligatorio mitigar la amenaza con MFA robusto, rate limiting, detección de patrones anómalos y contraseñas fuertes. CriptoCasa no puede aceptar ni transferir un riesgo que permite robos directos.</t>
+  </si>
+  <si>
+    <t>Fuga de datos KYC (Information Disclosure)</t>
+  </si>
+  <si>
+    <t>Los datos KYC incluyen información biométrica y documentación oficial. La regulación MiCA y AMLD6 obliga a protegerlos con cifrado, controles de acceso y auditoría estricta. Esta amenaza no se puede aceptar ni transferir, ya que un incumplimiento implica sanciones administrativas y daño reputacional grave.</t>
+  </si>
+  <si>
+    <t>Elevación de privilegios en el Panel Administrativo (EoP)</t>
+  </si>
+  <si>
+    <t>La escalada de privilegios permitiría modificar saldos, cuentas o auditorías. Se requiere una mitigación activa: MFA reforzado, RBAC estricto, segmentación de privilegios y revisión periódica de permisos. No se puede aceptar porque compromete activos financieros y la integridad del sistema.</t>
+  </si>
+  <si>
+    <t>La falta de integridad en logs incumple completamente MiCA, que exige trazabilidad total y disponibilidad de auditoría. La única opción válida es eliminar la vulnerabilidad, implementando logs inmutables (WORM), hashing, firmas digitales y segregación de permisos. No es válido mitigar parcialmente ni aceptar el riesgo.</t>
+  </si>
+  <si>
+    <t>Suplantación de identidad en el Servicio de Autenticación</t>
+  </si>
+  <si>
+    <t>Repudio de operaciones por logs incompletos</t>
+  </si>
+  <si>
+    <t>Fuga de datos desde el Chatbot LLM</t>
+  </si>
+  <si>
+    <t>DoS contra el API Gateway</t>
+  </si>
+  <si>
+    <t>Fuga de datos KYC durante la verificación</t>
+  </si>
+  <si>
+    <t>Elevación de privilegios en el Panel Administrativo</t>
+  </si>
+  <si>
+    <t>Manipulación en la BD de Usuarios</t>
+  </si>
+  <si>
+    <t>DoS contra el Servicio Wallet</t>
+  </si>
+  <si>
+    <t>RS-01</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El sistema deberá exigir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MFA obligatorio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> para todos los inicios de sesión y operaciones de retirada de fondos, usando factores independientes (TOTP o hardware token).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T-01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Acceso no autorizado / Suplantación)</t>
+    </r>
+  </si>
+  <si>
+    <t>Servicio de Autenticación</t>
+  </si>
+  <si>
+    <t>Prueba funcional de login y retirada + revisión de configuración MFA.</t>
+  </si>
+  <si>
+    <t>RS-02</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El Motor de Trading implementará </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>transacciones atómicas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y control de concurrencia (bloqueo optimista/pesimista) para evitar condiciones de carrera.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T-02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Inconsistencia de datos / Doble gasto)</t>
+    </r>
+  </si>
+  <si>
+    <t>Motor de Trading</t>
+  </si>
+  <si>
+    <t>Pruebas de estrés y concurrencia + revisión de código.</t>
+  </si>
+  <si>
+    <t>RS-03</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Los registros de auditoría se almacenarán en un sistema </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>inmutable (WORM)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> protegidos con hashing y sellos de tiempo.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Manipulación de logs / Repudio)</t>
+    </r>
+  </si>
+  <si>
+    <t>Base de Datos de Auditoría</t>
+  </si>
+  <si>
+    <t>Auditoría técnica + verificación de integridad mediante hash.</t>
+  </si>
+  <si>
+    <t>RS-04</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El Panel de Administración empleará </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RBAC estricto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, MFA reforzado y segregación de funciones (SoD).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T-07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Abuso de privilegios / Movimiento lateral)</t>
+    </r>
+  </si>
+  <si>
+    <t>Panel de Administración</t>
+  </si>
+  <si>
+    <t>Revisión de roles y permisos + pruebas de acceso.</t>
+  </si>
+  <si>
+    <t>RS-05</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Documentación KYC cifrada con </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TLS 1.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (tránsito) y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AES-256</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (reposo), con borrado automático según MiCA y AMLD6.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T-03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Exfiltración de datos / Incumplimiento legal)</t>
+    </r>
+  </si>
+  <si>
+    <t>Servicio KYC / Almacenamiento</t>
+  </si>
+  <si>
+    <t>Escaneo de cifrado + revisión de políticas de retención.</t>
+  </si>
+  <si>
+    <t>RS-06</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El pipeline CI/CD generará un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SBOM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> en cada build y verificará la firma e integridad de dependencias y contenedores.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T-11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Riesgos de Supply Chain / Inyección de malware)</t>
+    </r>
+  </si>
+  <si>
+    <t>Pipeline CI/CD</t>
+  </si>
+  <si>
+    <t>Revisión del pipeline + validación de integridad en build.</t>
+  </si>
+  <si>
+    <t>Escenario de Riesgo</t>
+  </si>
+  <si>
+    <t>Impacto Estimado</t>
+  </si>
+  <si>
+    <t>Medida de Control Propuesta</t>
+  </si>
+  <si>
+    <t>Código Riesgo</t>
+  </si>
+  <si>
+    <t>Escenario (Amenaza)</t>
+  </si>
+  <si>
+    <t>Control Propuesto</t>
+  </si>
+  <si>
+    <t>LLM01</t>
+  </si>
+  <si>
+    <t>LLM02</t>
+  </si>
+  <si>
+    <t>LLM03</t>
+  </si>
+  <si>
+    <t>LLM04</t>
+  </si>
+  <si>
+    <r>
+      <t>DNI, pasaporte, datos biométricos, dirección, email y número de teléfono de los usuarios,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fecha de nacimiento</t>
+    </r>
+  </si>
+  <si>
+    <t>Chatbot LLM expone datos mediante prompt injection</t>
+  </si>
+  <si>
+    <t>BAJO: Una caída del servicio de autenticación impide el acceso.</t>
+  </si>
+  <si>
+    <t>ALTO: La eliminación o modificación de los logs puede evitar encontrar un fallo en el sistema.</t>
+  </si>
+  <si>
+    <t>ALTO: La indisponibilidad de una clave puede interrumpir la comunicación entre servicios (caída parcial del sistema).</t>
+  </si>
+  <si>
+    <t>MUY ALTO: Puede dañar la confianza y llevar al fracaso del negocio.</t>
+  </si>
+  <si>
+    <t>CRÍTICO: La caída del servicio provoca pérdida de confianza, fuga de clientes  y posibles pérdidas.</t>
+  </si>
+  <si>
+    <t>MUY ALTO: Si no esta disponible la consulta de balances, se paralizan toda la operaciones de trading, depósitos y retiradas.</t>
+  </si>
+  <si>
+    <t>BAJO: Una caída del servicio de autenticación impediria el acceso pero no es un fallo critico. Aunque no es crítico para la seguridad, sí impacta la continuidad operativa temporalmente.</t>
+  </si>
+  <si>
+    <t>MEDIO: Si no estan disponibles los datos personales no se pueden registrar nuevos usuairos ni acceder a los datos los usuairos ya registrados puesto que no pueden iniciar sesión.</t>
+  </si>
+  <si>
+    <t>Manipulación de logs en la BD de Auditoría</t>
+  </si>
+  <si>
+    <t>Técnicas de prompt injection permiten manipular el comportamiento del LLM y obtener información privada.</t>
+  </si>
+  <si>
+    <t>Manipulación o eliminación de logs (Repudiation)</t>
+  </si>
+  <si>
+    <t>ELIMINAR</t>
+  </si>
+  <si>
+    <r>
+      <t>Dependencias de terceros vulnerables o maliciosas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Dependency confusion, typosquatting).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compromiso total del sistema pre-despliegue; inclusión de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>backdoors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o vulnerabilidades que se propagan a producción.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Generar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SBOM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en cada build; verificar firmas e integridad; usar repositorios privados (Proxy/Cache) y fijar versiones exactas (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pinning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Imágenes de contenedores desactualizadas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o con CVEs conocidos.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Explotación remota, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>escalada de privilegios</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o compromiso de microservicios internos mediante contenedores vulnerables.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Escaneo automático de imágenes (SCA) en el pipeline; uso de imágenes </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>distroless</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> o mínimas; política de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>parcheo obligatorio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposición de secretos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Claves API, tokens, contraseñas) en scripts o variables.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Acceso no autorizado a infraestructura crítica, manipulación del despliegue y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exfiltración de datos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sensibles.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uso de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Secret Managers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Vault, AWS Secrets Mgr); prohibir </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hardcoding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en el código; activar escaneo automático de secretos (Secret Scanning).</t>
+    </r>
+  </si>
+  <si>
+    <t>Pérdida de integridad en el modelo; respuestas maliciosas o erróneas diseñadas para engañar al usuario final.</t>
+  </si>
+  <si>
+    <t>Consumo Excesivo de Recursos (DoS): Envío de prompts extremadamente largos o complejos que saturan la capacidad de cómputo.</t>
+  </si>
+  <si>
+    <t>Indisponibilidad del servicio y costes operativos excesivos (facturación por tokens disparada).</t>
+  </si>
+  <si>
+    <r>
+      <t>Prompt Injection:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> El usuario introduce instrucciones ocultas para que el chatbot ignore restricciones y revele datos internos.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fuga de datos sensibles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, violación de normativas (GDPR/MiCA) y grave daño reputacional.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implementar filtros previos y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sanitización de prompts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; limitar el contexto accesible; usar respuestas basadas en plantillas seguras.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposición involuntaria de información:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> El LLM genera respuestas con datos personales o logs debido a un entrenamiento o contexto mal gestionado.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Riesgo legal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por divulgación de PII (Información de Identificación Personal) y exposición de secretos técnicos.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aplicar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>redacción segura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>output filtering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), anonimización automática y validación de respuestas (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>guardrails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) antes de la entrega.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Envenenamiento de Datos (Poisoning): Manipulación de los datos de entrenamiento o </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fine-tuning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para introducir sesgos o </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>backdoors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verificación de integridad de datasets; auditoría de fuentes de datos; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>entrenamiento en entornos aislados</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y controlados.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implementar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>límites de tokens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> por petición; cuotas de uso por usuario/API Key; monitorización de latencia y costes en tiempo real.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,6 +1782,81 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -473,7 +1932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -490,6 +1949,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -825,10 +2300,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4B2607-9765-4F28-A018-3C31E7FB2E62}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="41.81640625" customWidth="1"/>
+    <col min="1" max="1" width="46.1796875" customWidth="1"/>
+    <col min="2" max="2" width="139" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.90625" customWidth="1"/>
+    <col min="4" max="4" width="172.54296875" customWidth="1"/>
+    <col min="5" max="5" width="174.26953125" customWidth="1"/>
+    <col min="6" max="6" width="154.453125" customWidth="1"/>
     <col min="7" max="7" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -854,162 +2334,182 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>42</v>
+        <v>300</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>45</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>49</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>60</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>70</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>77</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>84</v>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1017,476 +2517,161 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C604E5F-CEB9-4052-A7F8-136A8B60665B}">
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="8" width="27.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C39C7C-8AA4-4B22-B5BD-97B7A98EB48F}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="3" width="42.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C09D12C1-A07A-4D69-8B79-31F71DB67A7B}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="2" width="21.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4043CF6A-2B3D-4FFA-AF3B-D7EA33064A56}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="5" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90C8F9AD-8E74-4CC3-B81E-F70C1121FFF7}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="45.08984375" customWidth="1"/>
-    <col min="4" max="4" width="70.08984375" customWidth="1"/>
+    <col min="1" max="3" width="45.1796875" customWidth="1"/>
+    <col min="4" max="4" width="70.1796875" customWidth="1"/>
     <col min="5" max="5" width="110" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1579,4 +2764,1112 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C604E5F-CEB9-4052-A7F8-136A8B60665B}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.1796875" customWidth="1"/>
+    <col min="2" max="2" width="39.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="255.6328125" customWidth="1"/>
+    <col min="5" max="5" width="46.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="91.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="147.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:8" s="17" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F7B112-5CF8-B94B-8406-3FF34FFFEB11}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.08984375" customWidth="1"/>
+    <col min="3" max="3" width="37.36328125" customWidth="1"/>
+    <col min="4" max="4" width="44.7265625" customWidth="1"/>
+    <col min="5" max="5" width="64.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF76EC0-A0A5-6441-9976-4B486FE62B34}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="109.453125" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C39C7C-8AA4-4B22-B5BD-97B7A98EB48F}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.453125" customWidth="1"/>
+    <col min="2" max="2" width="48.90625" customWidth="1"/>
+    <col min="3" max="3" width="52.90625" customWidth="1"/>
+    <col min="4" max="4" width="126.08984375" customWidth="1"/>
+    <col min="5" max="5" width="38.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C09D12C1-A07A-4D69-8B79-31F71DB67A7B}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.26953125" customWidth="1"/>
+    <col min="3" max="3" width="45.81640625" customWidth="1"/>
+    <col min="4" max="4" width="255.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4043CF6A-2B3D-4FFA-AF3B-D7EA33064A56}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="144.7265625" customWidth="1"/>
+    <col min="3" max="3" width="49.36328125" customWidth="1"/>
+    <col min="4" max="4" width="28.08984375" customWidth="1"/>
+    <col min="5" max="5" width="57.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B12" s="15"/>
+    </row>
+    <row r="14" spans="1:5" ht="20.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="16"/>
+    </row>
+    <row r="16" spans="1:5" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="10"/>
+    </row>
+    <row r="18" spans="2:2" ht="20.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="16"/>
+    </row>
+    <row r="20" spans="2:2" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="10"/>
+    </row>
+    <row r="22" spans="2:2" ht="20.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="16"/>
+    </row>
+    <row r="24" spans="2:2" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F5D75B-2049-1C48-8554-D5CBE5CA3C41}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="81.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105.7265625" customWidth="1"/>
+    <col min="3" max="3" width="124.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8856480-FA05-E445-9D8B-B5767A2DF515}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="129" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="113.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>